--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,1380 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130334296</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91110</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497199</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6587175</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Drejby, Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130335392</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497257</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6587579</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130334312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93010</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497197</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6587165</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130335441</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6587615</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130335105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497228</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6587320</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130335274</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källtorpet, Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497259</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6587399</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130334499</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497173</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6587272</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130335768</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6587614</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130334623</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497215</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6587309</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Drejby, Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130335421</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497262</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6587585</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130334482</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497192</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6587259</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130335765</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6587614</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130334552</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497171</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6587294</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91110</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>91110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,52 +989,57 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2164,6 +2164,148 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130335126</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497211</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6587320</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>91110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91110</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91110</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>91113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,52 +989,57 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>93013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>91139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91113</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,57 +989,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>93039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R5" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>93013</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R6" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>130334499</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>91139</v>
+        <v>91140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91140</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>91141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,52 +989,57 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B5" t="n">
-        <v>93040</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>93041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130335768</v>
+        <v>130334623</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497253</v>
+        <v>497215</v>
       </c>
       <c r="R10" t="n">
-        <v>6587614</v>
+        <v>6587309</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334623</v>
+        <v>130335421</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497215</v>
+        <v>497262</v>
       </c>
       <c r="R11" t="n">
-        <v>6587309</v>
+        <v>6587585</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335421</v>
+        <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497262</v>
+        <v>497253</v>
       </c>
       <c r="R12" t="n">
-        <v>6587585</v>
+        <v>6587614</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>91143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman, Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91141</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,57 +989,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>93043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R5" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>93041</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R6" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>130334499</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334623</v>
+        <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497215</v>
+        <v>497253</v>
       </c>
       <c r="R10" t="n">
-        <v>6587309</v>
+        <v>6587614</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130335421</v>
+        <v>130334623</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497262</v>
+        <v>497215</v>
       </c>
       <c r="R11" t="n">
-        <v>6587585</v>
+        <v>6587309</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman, Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335768</v>
+        <v>130335421</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497253</v>
+        <v>497262</v>
       </c>
       <c r="R12" t="n">
-        <v>6587614</v>
+        <v>6587585</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91143</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Mattias Drejby</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>91143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130335768</v>
+        <v>130334623</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497253</v>
+        <v>497215</v>
       </c>
       <c r="R10" t="n">
-        <v>6587614</v>
+        <v>6587309</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334623</v>
+        <v>130335421</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497215</v>
+        <v>497262</v>
       </c>
       <c r="R11" t="n">
-        <v>6587309</v>
+        <v>6587585</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Mattias Drejby</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335421</v>
+        <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497262</v>
+        <v>497253</v>
       </c>
       <c r="R12" t="n">
-        <v>6587585</v>
+        <v>6587614</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>91143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91143</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,52 +989,57 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B5" t="n">
-        <v>93047</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>93047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334623</v>
+        <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497215</v>
+        <v>497253</v>
       </c>
       <c r="R10" t="n">
-        <v>6587309</v>
+        <v>6587614</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130335421</v>
+        <v>130334623</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497262</v>
+        <v>497215</v>
       </c>
       <c r="R11" t="n">
-        <v>6587585</v>
+        <v>6587309</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335768</v>
+        <v>130335421</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497253</v>
+        <v>497262</v>
       </c>
       <c r="R12" t="n">
-        <v>6587614</v>
+        <v>6587585</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91143</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>91143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,57 +989,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>93047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R5" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>93047</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R6" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1636,7 +1636,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334623</v>
+        <v>130335421</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497215</v>
+        <v>497262</v>
       </c>
       <c r="R11" t="n">
-        <v>6587309</v>
+        <v>6587585</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,14 +1731,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335421</v>
+        <v>130334623</v>
       </c>
       <c r="B12" t="n">
         <v>5177</v>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497262</v>
+        <v>497215</v>
       </c>
       <c r="R12" t="n">
-        <v>6587585</v>
+        <v>6587309</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130335768</v>
+        <v>130334623</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497253</v>
+        <v>497215</v>
       </c>
       <c r="R10" t="n">
-        <v>6587614</v>
+        <v>6587309</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1738,50 +1738,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334623</v>
+        <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497215</v>
+        <v>497253</v>
       </c>
       <c r="R12" t="n">
-        <v>6587309</v>
+        <v>6587614</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>91155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91143</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>130334499</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334623</v>
+        <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497215</v>
+        <v>497253</v>
       </c>
       <c r="R10" t="n">
-        <v>6587309</v>
+        <v>6587614</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130335421</v>
+        <v>130334623</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497262</v>
+        <v>497215</v>
       </c>
       <c r="R11" t="n">
-        <v>6587585</v>
+        <v>6587309</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335768</v>
+        <v>130335421</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497253</v>
+        <v>497262</v>
       </c>
       <c r="R12" t="n">
-        <v>6587614</v>
+        <v>6587585</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>91155</v>
+        <v>91156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>130334499</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003655</v>
       </c>
       <c r="B2" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>91156</v>
+        <v>91157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B5" t="n">
-        <v>93061</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>93062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>130334499</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130335768</v>
+        <v>130334623</v>
       </c>
       <c r="B10" t="n">
-        <v>57860</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497253</v>
+        <v>497215</v>
       </c>
       <c r="R10" t="n">
-        <v>6587614</v>
+        <v>6587309</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334623</v>
+        <v>130335421</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497215</v>
+        <v>497262</v>
       </c>
       <c r="R11" t="n">
-        <v>6587309</v>
+        <v>6587585</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335421</v>
+        <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>57861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497262</v>
+        <v>497253</v>
       </c>
       <c r="R12" t="n">
-        <v>6587585</v>
+        <v>6587614</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B3" t="n">
-        <v>91157</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R3" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,11 +870,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,57 +887,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>91157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,6 +967,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,57 +989,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130335441</v>
+        <v>130334312</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>93062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497242</v>
+        <v>497197</v>
       </c>
       <c r="R5" t="n">
-        <v>6587615</v>
+        <v>6587165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130334312</v>
+        <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>93062</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497197</v>
+        <v>497242</v>
       </c>
       <c r="R6" t="n">
-        <v>6587165</v>
+        <v>6587615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334623</v>
+        <v>130335768</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497215</v>
+        <v>497253</v>
       </c>
       <c r="R10" t="n">
-        <v>6587309</v>
+        <v>6587614</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130335421</v>
+        <v>130334623</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497262</v>
+        <v>497215</v>
       </c>
       <c r="R11" t="n">
-        <v>6587585</v>
+        <v>6587309</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335768</v>
+        <v>130335421</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497253</v>
+        <v>497262</v>
       </c>
       <c r="R12" t="n">
-        <v>6587614</v>
+        <v>6587585</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335392</v>
+        <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>91157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497257</v>
+        <v>497199</v>
       </c>
       <c r="R3" t="n">
-        <v>6587579</v>
+        <v>6587175</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,6 +865,11 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130334296</v>
+        <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>91157</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497199</v>
+        <v>497257</v>
       </c>
       <c r="R4" t="n">
-        <v>6587175</v>
+        <v>6587579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,11 +972,6 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -1534,50 +1534,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130335768</v>
+        <v>130334623</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497253</v>
+        <v>497215</v>
       </c>
       <c r="R10" t="n">
-        <v>6587614</v>
+        <v>6587309</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Mattias Drejby, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334623</v>
+        <v>130335421</v>
       </c>
       <c r="B11" t="n">
         <v>5177</v>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497215</v>
+        <v>497262</v>
       </c>
       <c r="R11" t="n">
-        <v>6587309</v>
+        <v>6587585</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,45 +1731,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335421</v>
+        <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>57861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497262</v>
+        <v>497253</v>
       </c>
       <c r="R12" t="n">
-        <v>6587585</v>
+        <v>6587614</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>130335392</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130335441</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130335105</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130335768</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>130334482</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>130334552</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130335126</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130003655</v>
+        <v>130334312</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497213</v>
+        <v>497197</v>
       </c>
       <c r="R2" t="n">
-        <v>6587143</v>
+        <v>6587165</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +766,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +785,7 @@
         <v>130334296</v>
       </c>
       <c r="B3" t="n">
-        <v>91157</v>
+        <v>91282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,14 +884,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335392</v>
+        <v>130334482</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,17 +920,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497257</v>
+        <v>497192</v>
       </c>
       <c r="R4" t="n">
-        <v>6587579</v>
+        <v>6587259</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130334312</v>
+        <v>130334552</v>
       </c>
       <c r="B5" t="n">
-        <v>93062</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497197</v>
+        <v>497171</v>
       </c>
       <c r="R5" t="n">
-        <v>6587165</v>
+        <v>6587294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1108,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335441</v>
+        <v>130335105</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1132,24 +1137,27 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497242</v>
+        <v>497228</v>
       </c>
       <c r="R6" t="n">
-        <v>6587615</v>
+        <v>6587320</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,19 +1184,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,26 +1201,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130335105</v>
+        <v>130335126</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1244,27 +1242,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497228</v>
+        <v>497211</v>
       </c>
       <c r="R7" t="n">
         <v>6587320</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,11 +1286,26 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1304,16 +1314,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1323,11 +1358,11 @@
         <v>130335274</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1422,27 +1457,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130334499</v>
+        <v>130335392</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1458,17 +1493,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497173</v>
+        <v>497257</v>
       </c>
       <c r="R9" t="n">
-        <v>6587272</v>
+        <v>6587579</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1530,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,22 +1547,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334623</v>
+        <v>130335441</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,42 +1570,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497215</v>
+        <v>497242</v>
       </c>
       <c r="R10" t="n">
-        <v>6587309</v>
+        <v>6587615</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,9 +1632,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,22 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby, Lotta Sörman</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130335421</v>
+        <v>130335768</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,27 +1682,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1676,13 +1711,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497262</v>
+        <v>497253</v>
       </c>
       <c r="R11" t="n">
-        <v>6587585</v>
+        <v>6587614</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130335768</v>
+        <v>130334499</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,16 +1784,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1774,17 +1809,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497253</v>
+        <v>497173</v>
       </c>
       <c r="R12" t="n">
-        <v>6587614</v>
+        <v>6587272</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,9 +1846,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,50 +1873,50 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130334482</v>
+        <v>130334623</v>
       </c>
       <c r="B13" t="n">
-        <v>57889</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,13 +1925,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497192</v>
+        <v>497215</v>
       </c>
       <c r="R13" t="n">
-        <v>6587259</v>
+        <v>6587309</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,19 +1958,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,22 +1975,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Lotta Sörman, Mattias Drejby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130335765</v>
+        <v>130335421</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,7 +2018,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1992,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497253</v>
+        <v>497262</v>
       </c>
       <c r="R14" t="n">
-        <v>6587614</v>
+        <v>6587585</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,53 +2089,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130334552</v>
+        <v>130335765</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Nedre Källtorpet, Nedre Källtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497171</v>
+        <v>497253</v>
       </c>
       <c r="R15" t="n">
-        <v>6587294</v>
+        <v>6587614</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2127,19 +2162,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,39 +2179,39 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130335126</v>
+        <v>130003655</v>
       </c>
       <c r="B16" t="n">
-        <v>57889</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,22 +2222,22 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497211</v>
+        <v>497213</v>
       </c>
       <c r="R16" t="n">
-        <v>6587320</v>
+        <v>6587143</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,27 +2261,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,26 +2291,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 56956-2025 artfynd.xlsx
+++ b/artfynd/A 56956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334312</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334552</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335105</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335126</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335274</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335392</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335441</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334499</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334623</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335421</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335765</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,8 +2380,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130003655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>